--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J350"/>
+  <dimension ref="A1:J353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13036,6 +13036,114 @@
         <v>393.51</v>
       </c>
       <c r="J350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="C351" t="n">
+        <v>388.63</v>
+      </c>
+      <c r="D351" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="E351" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="F351" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="G351" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="H351" t="n">
+        <v>386.51</v>
+      </c>
+      <c r="I351" t="n">
+        <v>394.17</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>386.33</v>
+      </c>
+      <c r="C352" t="n">
+        <v>389.25</v>
+      </c>
+      <c r="D352" t="n">
+        <v>390.51</v>
+      </c>
+      <c r="E352" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="F352" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="G352" t="n">
+        <v>382.88</v>
+      </c>
+      <c r="H352" t="n">
+        <v>386.58</v>
+      </c>
+      <c r="I352" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="C353" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="D353" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="E353" t="n">
+        <v>384.46</v>
+      </c>
+      <c r="F353" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="G353" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="H353" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="I353" t="n">
+        <v>393.34</v>
+      </c>
+      <c r="J353" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13052,7 +13160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16705,6 +16813,36 @@
       </c>
       <c r="B365" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -16873,28 +17011,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1154761865320747</v>
+        <v>-0.1232307952388786</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0460426845742633</v>
+        <v>0.05241791082300329</v>
       </c>
       <c r="M2" t="n">
-        <v>2.674077230387254</v>
+        <v>2.686508776451236</v>
       </c>
       <c r="N2" t="n">
-        <v>15.72232283441463</v>
+        <v>15.77681939666255</v>
       </c>
       <c r="O2" t="n">
-        <v>3.965138438240792</v>
+        <v>3.972004455770732</v>
       </c>
       <c r="P2" t="n">
-        <v>394.0595236139955</v>
+        <v>394.1415808639988</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16951,28 +17089,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1439412352582168</v>
+        <v>-0.1493510267404685</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08540398621195711</v>
+        <v>0.09227284646896272</v>
       </c>
       <c r="M3" t="n">
-        <v>2.509032918367049</v>
+        <v>2.510438317808927</v>
       </c>
       <c r="N3" t="n">
-        <v>12.6265630304457</v>
+        <v>12.61077131697212</v>
       </c>
       <c r="O3" t="n">
-        <v>3.553387542957523</v>
+        <v>3.551164783134138</v>
       </c>
       <c r="P3" t="n">
-        <v>396.3133686880891</v>
+        <v>396.3706135586895</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17029,28 +17167,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04721539938069404</v>
+        <v>-0.05394287123714798</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01121281012570718</v>
+        <v>0.0146704255810387</v>
       </c>
       <c r="M4" t="n">
-        <v>2.60552918111254</v>
+        <v>2.616052383362498</v>
       </c>
       <c r="N4" t="n">
-        <v>11.18714420863929</v>
+        <v>11.23183564774923</v>
       </c>
       <c r="O4" t="n">
-        <v>3.344718853452303</v>
+        <v>3.351393090604148</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8236758583312</v>
+        <v>395.8948719542411</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17107,28 +17245,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09063559024438575</v>
+        <v>-0.1057116324718355</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02580118774695839</v>
+        <v>0.03407835525469549</v>
       </c>
       <c r="M5" t="n">
-        <v>3.330850026386648</v>
+        <v>3.387454753977188</v>
       </c>
       <c r="N5" t="n">
-        <v>17.650985953132</v>
+        <v>18.20340565888222</v>
       </c>
       <c r="O5" t="n">
-        <v>4.201307647998656</v>
+        <v>4.26654493224696</v>
       </c>
       <c r="P5" t="n">
-        <v>396.0234202636566</v>
+        <v>396.1829649293246</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17185,28 +17323,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09512302507368812</v>
+        <v>-0.1095723372128968</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02641603778276469</v>
+        <v>0.03424779891301943</v>
       </c>
       <c r="M6" t="n">
-        <v>3.497790354390093</v>
+        <v>3.54926572718087</v>
       </c>
       <c r="N6" t="n">
-        <v>18.79548324882196</v>
+        <v>19.27150937206738</v>
       </c>
       <c r="O6" t="n">
-        <v>4.335375790957683</v>
+        <v>4.389932729788394</v>
       </c>
       <c r="P6" t="n">
-        <v>395.680962916335</v>
+        <v>395.8349390021834</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17263,28 +17401,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1203680031321205</v>
+        <v>-0.132079551300779</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04193943978045367</v>
+        <v>0.04988431990362319</v>
       </c>
       <c r="M7" t="n">
-        <v>3.397381638664366</v>
+        <v>3.433691480828288</v>
       </c>
       <c r="N7" t="n">
-        <v>18.65386823868947</v>
+        <v>18.91317484950826</v>
       </c>
       <c r="O7" t="n">
-        <v>4.319012414741299</v>
+        <v>4.348928011534366</v>
       </c>
       <c r="P7" t="n">
-        <v>392.9718992008436</v>
+        <v>393.0967028540244</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17341,28 +17479,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1665428174527154</v>
+        <v>-0.1718573659688618</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1158082686960631</v>
+        <v>0.1236106606061111</v>
       </c>
       <c r="M8" t="n">
-        <v>2.734533561500066</v>
+        <v>2.741475801118551</v>
       </c>
       <c r="N8" t="n">
-        <v>11.93534977858549</v>
+        <v>11.91950716235192</v>
       </c>
       <c r="O8" t="n">
-        <v>3.454757557135593</v>
+        <v>3.45246392629263</v>
       </c>
       <c r="P8" t="n">
-        <v>394.1830738073775</v>
+        <v>394.2397074467425</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17419,28 +17557,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1675827121449119</v>
+        <v>-0.1700822580863506</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07771675789034826</v>
+        <v>0.08114618738817136</v>
       </c>
       <c r="M9" t="n">
-        <v>3.444232293600034</v>
+        <v>3.427372586018826</v>
       </c>
       <c r="N9" t="n">
-        <v>18.96581937212141</v>
+        <v>18.82522365394853</v>
       </c>
       <c r="O9" t="n">
-        <v>4.354976391683588</v>
+        <v>4.338804403744023</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5632236122794</v>
+        <v>399.5896801676982</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17478,7 +17616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J350"/>
+  <dimension ref="A1:J353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35669,6 +35807,162 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-36.60211313797701,175.54312049247903</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-36.60255681399256,175.5436790380547</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-36.60276741077823,175.54444263860114</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-36.60298797651555,175.5452535551657</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-36.60302966202996,175.54611162394968</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-36.603028545507904,175.54698302190488</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-36.602896576384474,175.54783220323642</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-36.602650334829214,175.54865950448675</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-36.60210802779551,175.5431269537339</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-36.602552097702684,175.54368275001738</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-36.60276767007312,175.54444254400988</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-36.60298851216966,175.54525346507563</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-36.603030743142746,175.5461116236438</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-36.603027649326734,175.54698290736422</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-36.60289596083776,175.5478320330887</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-36.602659523518795,175.54866273085793</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-36.60210487336233,175.54313094216238</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-36.602549739557716,175.54368460599855</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-36.60276948513737,175.54444188187122</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-36.60298726231007,175.54525367528578</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-36.603031013420946,175.54611162356733</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-36.603032847177424,175.5469835717001</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-36.60289754367216,175.54783247061138</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-36.60265752974654,175.54866203079618</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13146,6 +13146,42 @@
       <c r="J353" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="C354" t="n">
+        <v>391</v>
+      </c>
+      <c r="D354" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="E354" t="n">
+        <v>385.34</v>
+      </c>
+      <c r="F354" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="G354" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="H354" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="I354" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16843,6 +16879,16 @@
       </c>
       <c r="B368" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -17011,28 +17057,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1232307952388786</v>
+        <v>-0.1244381598607997</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05241791082300329</v>
+        <v>0.05365646213251607</v>
       </c>
       <c r="M2" t="n">
-        <v>2.686508776451236</v>
+        <v>2.684463761657493</v>
       </c>
       <c r="N2" t="n">
-        <v>15.77681939666255</v>
+        <v>15.74599240648934</v>
       </c>
       <c r="O2" t="n">
-        <v>3.972004455770732</v>
+        <v>3.968122025151109</v>
       </c>
       <c r="P2" t="n">
-        <v>394.1415808639988</v>
+        <v>394.1543828480401</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17089,28 +17135,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1493510267404685</v>
+        <v>-0.1500859341459424</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09227284646896272</v>
+        <v>0.09357521694264237</v>
       </c>
       <c r="M3" t="n">
-        <v>2.510438317808927</v>
+        <v>2.506469935969733</v>
       </c>
       <c r="N3" t="n">
-        <v>12.61077131697212</v>
+        <v>12.58018431050212</v>
       </c>
       <c r="O3" t="n">
-        <v>3.551164783134138</v>
+        <v>3.546855552528482</v>
       </c>
       <c r="P3" t="n">
-        <v>396.3706135586895</v>
+        <v>396.3784059626623</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17167,28 +17213,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05394287123714798</v>
+        <v>-0.05544880728616276</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0146704255810387</v>
+        <v>0.01555103549237002</v>
       </c>
       <c r="M4" t="n">
-        <v>2.616052383362498</v>
+        <v>2.616037605842494</v>
       </c>
       <c r="N4" t="n">
-        <v>11.23183564774923</v>
+        <v>11.22159011941726</v>
       </c>
       <c r="O4" t="n">
-        <v>3.351393090604148</v>
+        <v>3.349864194175229</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8948719542411</v>
+        <v>395.9108397645583</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17245,28 +17291,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1057116324718355</v>
+        <v>-0.1100568410492174</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03407835525469549</v>
+        <v>0.03669748280083307</v>
       </c>
       <c r="M5" t="n">
-        <v>3.387454753977188</v>
+        <v>3.40264341665053</v>
       </c>
       <c r="N5" t="n">
-        <v>18.20340565888222</v>
+        <v>18.3314405960051</v>
       </c>
       <c r="O5" t="n">
-        <v>4.26654493224696</v>
+        <v>4.281523163081697</v>
       </c>
       <c r="P5" t="n">
-        <v>396.1829649293246</v>
+        <v>396.2290382445877</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17323,28 +17369,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1095723372128968</v>
+        <v>-0.113624013040872</v>
       </c>
       <c r="J6" t="n">
+        <v>353</v>
+      </c>
+      <c r="K6" t="n">
         <v>352</v>
       </c>
-      <c r="K6" t="n">
-        <v>351</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03424779891301943</v>
+        <v>0.03666499412797397</v>
       </c>
       <c r="M6" t="n">
-        <v>3.54926572718087</v>
+        <v>3.562082491686575</v>
       </c>
       <c r="N6" t="n">
-        <v>19.27150937206738</v>
+        <v>19.37076784662342</v>
       </c>
       <c r="O6" t="n">
-        <v>4.389932729788394</v>
+        <v>4.401223448840495</v>
       </c>
       <c r="P6" t="n">
-        <v>395.8349390021834</v>
+        <v>395.8781977651777</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17401,28 +17447,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.132079551300779</v>
+        <v>-0.1353575594068546</v>
       </c>
       <c r="J7" t="n">
+        <v>353</v>
+      </c>
+      <c r="K7" t="n">
         <v>352</v>
       </c>
-      <c r="K7" t="n">
-        <v>351</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.04988431990362319</v>
+        <v>0.05229669006149773</v>
       </c>
       <c r="M7" t="n">
-        <v>3.433691480828288</v>
+        <v>3.442352472611673</v>
       </c>
       <c r="N7" t="n">
-        <v>18.91317484950826</v>
+        <v>18.96025139321145</v>
       </c>
       <c r="O7" t="n">
-        <v>4.348928011534366</v>
+        <v>4.354337078501324</v>
       </c>
       <c r="P7" t="n">
-        <v>393.0967028540244</v>
+        <v>393.1317013538489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17479,28 +17525,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1718573659688618</v>
+        <v>-0.1733326585828308</v>
       </c>
       <c r="J8" t="n">
+        <v>353</v>
+      </c>
+      <c r="K8" t="n">
         <v>352</v>
       </c>
-      <c r="K8" t="n">
-        <v>351</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1236106606061111</v>
+        <v>0.1259529327788426</v>
       </c>
       <c r="M8" t="n">
-        <v>2.741475801118551</v>
+        <v>2.742196789256025</v>
       </c>
       <c r="N8" t="n">
-        <v>11.91950716235192</v>
+        <v>11.90606360520624</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45246392629263</v>
+        <v>3.450516425871096</v>
       </c>
       <c r="P8" t="n">
-        <v>394.2397074467425</v>
+        <v>394.2554587892102</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17557,28 +17603,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1700822580863506</v>
+        <v>-0.170370028352677</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08114618738817136</v>
+        <v>0.08184846154708114</v>
       </c>
       <c r="M9" t="n">
-        <v>3.427372586018826</v>
+        <v>3.419092084002049</v>
       </c>
       <c r="N9" t="n">
-        <v>18.82522365394853</v>
+        <v>18.77268214927411</v>
       </c>
       <c r="O9" t="n">
-        <v>4.338804403744023</v>
+        <v>4.33274533630516</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5896801676982</v>
+        <v>399.59273146661</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17616,7 +17662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35963,6 +36009,58 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-36.60209364357919,175.54314514096518</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-36.60253878559366,175.543693227329</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-36.602757644003844,175.5444462015372</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-36.60297940604985,175.54525499660653</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-36.60302047257128,175.5461116265496</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-36.60302155529488,175.5469821284878</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-36.6028928831042,175.54783118235022</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-36.602647560885174,175.54865853048804</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0140/nzd0140.xlsx
+++ b/data/nzd0140/nzd0140.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13182,6 +13182,42 @@
       <c r="J354" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="C355" t="n">
+        <v>390.48</v>
+      </c>
+      <c r="D355" t="n">
+        <v>390.95</v>
+      </c>
+      <c r="E355" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="F355" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="G355" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="H355" t="n">
+        <v>386.16</v>
+      </c>
+      <c r="I355" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16889,6 +16925,16 @@
       </c>
       <c r="B369" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -17057,28 +17103,28 @@
         <v>0.1057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1244381598607997</v>
+        <v>-0.1255288210408668</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05365646213251607</v>
+        <v>0.05482744470542877</v>
       </c>
       <c r="M2" t="n">
-        <v>2.684463761657493</v>
+        <v>2.681879382618637</v>
       </c>
       <c r="N2" t="n">
-        <v>15.74599240648934</v>
+        <v>15.71277412451826</v>
       </c>
       <c r="O2" t="n">
-        <v>3.968122025151109</v>
+        <v>3.963934172576313</v>
       </c>
       <c r="P2" t="n">
-        <v>394.1543828480401</v>
+        <v>394.1660031688201</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17135,28 +17181,28 @@
         <v>0.1009</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1500859341459424</v>
+        <v>-0.1510886620216448</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09357521694264237</v>
+        <v>0.09516914104742769</v>
       </c>
       <c r="M3" t="n">
-        <v>2.506469935969733</v>
+        <v>2.503612955180821</v>
       </c>
       <c r="N3" t="n">
-        <v>12.58018431050212</v>
+        <v>12.55416623493153</v>
       </c>
       <c r="O3" t="n">
-        <v>3.546855552528482</v>
+        <v>3.543185887719063</v>
       </c>
       <c r="P3" t="n">
-        <v>396.3784059626623</v>
+        <v>396.3890894084325</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17213,28 +17259,28 @@
         <v>0.1948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05544880728616276</v>
+        <v>-0.05733040731735847</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01555103549237002</v>
+        <v>0.01665724000215307</v>
       </c>
       <c r="M4" t="n">
-        <v>2.616037605842494</v>
+        <v>2.617775730185081</v>
       </c>
       <c r="N4" t="n">
-        <v>11.22159011941726</v>
+        <v>11.22340943410933</v>
       </c>
       <c r="O4" t="n">
-        <v>3.349864194175229</v>
+        <v>3.350135733684432</v>
       </c>
       <c r="P4" t="n">
-        <v>395.9108397645583</v>
+        <v>395.9308870499499</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17291,28 +17337,28 @@
         <v>0.1976</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1100568410492174</v>
+        <v>-0.1152745035870335</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03669748280083307</v>
+        <v>0.03981313383274632</v>
       </c>
       <c r="M5" t="n">
-        <v>3.40264341665053</v>
+        <v>3.423316319682084</v>
       </c>
       <c r="N5" t="n">
-        <v>18.3314405960051</v>
+        <v>18.53739863130836</v>
       </c>
       <c r="O5" t="n">
-        <v>4.281523163081697</v>
+        <v>4.305507941150307</v>
       </c>
       <c r="P5" t="n">
-        <v>396.2290382445877</v>
+        <v>396.2846292141023</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17369,28 +17415,28 @@
         <v>0.1302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.113624013040872</v>
+        <v>-0.1183920836356002</v>
       </c>
       <c r="J6" t="n">
+        <v>354</v>
+      </c>
+      <c r="K6" t="n">
         <v>353</v>
       </c>
-      <c r="K6" t="n">
-        <v>352</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03666499412797397</v>
+        <v>0.03949910975507209</v>
       </c>
       <c r="M6" t="n">
-        <v>3.562082491686575</v>
+        <v>3.578934862109486</v>
       </c>
       <c r="N6" t="n">
-        <v>19.37076784662342</v>
+        <v>19.52816355059123</v>
       </c>
       <c r="O6" t="n">
-        <v>4.401223448840495</v>
+        <v>4.419068176730388</v>
       </c>
       <c r="P6" t="n">
-        <v>395.8781977651777</v>
+        <v>395.9293487653035</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17447,28 +17493,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1353575594068546</v>
+        <v>-0.1396836733354339</v>
       </c>
       <c r="J7" t="n">
+        <v>354</v>
+      </c>
+      <c r="K7" t="n">
         <v>353</v>
       </c>
-      <c r="K7" t="n">
-        <v>352</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05229669006149773</v>
+        <v>0.05534309506050827</v>
       </c>
       <c r="M7" t="n">
-        <v>3.442352472611673</v>
+        <v>3.456993088095047</v>
       </c>
       <c r="N7" t="n">
-        <v>18.96025139321145</v>
+        <v>19.08128271454147</v>
       </c>
       <c r="O7" t="n">
-        <v>4.354337078501324</v>
+        <v>4.368212759761304</v>
       </c>
       <c r="P7" t="n">
-        <v>393.1317013538489</v>
+        <v>393.1781111226869</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17525,28 +17571,28 @@
         <v>0.1395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1733326585828308</v>
+        <v>-0.1752070676947151</v>
       </c>
       <c r="J8" t="n">
+        <v>354</v>
+      </c>
+      <c r="K8" t="n">
         <v>353</v>
       </c>
-      <c r="K8" t="n">
-        <v>352</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1259529327788426</v>
+        <v>0.1287164019956987</v>
       </c>
       <c r="M8" t="n">
-        <v>2.742196789256025</v>
+        <v>2.745240251899645</v>
       </c>
       <c r="N8" t="n">
-        <v>11.90606360520624</v>
+        <v>11.90513983712127</v>
       </c>
       <c r="O8" t="n">
-        <v>3.450516425871096</v>
+        <v>3.450382563879152</v>
       </c>
       <c r="P8" t="n">
-        <v>394.2554587892102</v>
+        <v>394.2755671116047</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17603,28 +17649,28 @@
         <v>0.1819</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.170370028352677</v>
+        <v>-0.170942343509041</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08184846154708114</v>
+        <v>0.0828028292751295</v>
       </c>
       <c r="M9" t="n">
-        <v>3.419092084002049</v>
+        <v>3.41223653988704</v>
       </c>
       <c r="N9" t="n">
-        <v>18.77268214927411</v>
+        <v>18.72275298480859</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33274533630516</v>
+        <v>4.326979660780553</v>
       </c>
       <c r="P9" t="n">
-        <v>399.59273146661</v>
+        <v>399.5988291308763</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17662,7 +17708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36061,6 +36107,58 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-36.602092507983066,175.54314657679893</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-36.60254274119185,175.54369011407107</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-36.60276386708133,175.54444393134796</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-36.60299440436481,175.54525247408492</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-36.60303281527559,175.54611162305756</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-36.60303921006359,175.54698438493907</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-36.60289965411802,175.54783305397498</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-36.60265232860149,175.54866020454833</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
